--- a/city_finance_analysis/data_clean/住宅商品房销售总额.xlsx
+++ b/city_finance_analysis/data_clean/住宅商品房销售总额.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,194 +417,194 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>天津</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>石家庄</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>太原</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>呼和浩特</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>沈阳</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>大连</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>长春</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>哈尔滨</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>宁波</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>合肥</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>福州</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>厦门</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>南昌</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>济南</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>青岛</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>郑州</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>长沙</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>南宁</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>海口</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>贵阳</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>昆明</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>拉萨</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>西安</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>兰州</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>西宁</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>银川</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>乌鲁木齐</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>2006</v>
       </c>
       <c r="B2" t="n">
@@ -727,7 +715,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2007</v>
       </c>
       <c r="B3" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2008</v>
       </c>
       <c r="B4" t="n">
@@ -949,7 +937,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>2009</v>
       </c>
       <c r="B5" t="n">
@@ -1060,7 +1048,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>2010</v>
       </c>
       <c r="B6" t="n">
@@ -1171,7 +1159,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>2011</v>
       </c>
       <c r="B7" t="n">
@@ -1282,7 +1270,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>2012</v>
       </c>
       <c r="B8" t="n">
@@ -1393,7 +1381,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>2013</v>
       </c>
       <c r="B9" t="n">
@@ -1504,7 +1492,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>2014</v>
       </c>
       <c r="B10" t="n">
@@ -1615,7 +1603,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>2015</v>
       </c>
       <c r="B11" t="n">
@@ -1726,7 +1714,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>2016</v>
       </c>
       <c r="B12" t="n">
@@ -1837,7 +1825,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>2017</v>
       </c>
       <c r="B13" t="n">
@@ -1948,7 +1936,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>2018</v>
       </c>
       <c r="B14" t="n">
@@ -2059,7 +2047,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>2019</v>
       </c>
       <c r="B15" t="n">
@@ -2170,7 +2158,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>2020</v>
       </c>
       <c r="B16" t="n">
@@ -2281,7 +2269,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>2021</v>
       </c>
       <c r="B17" t="n">
@@ -2392,7 +2380,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>2022</v>
       </c>
       <c r="B18" t="n">
@@ -2503,7 +2491,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>2023</v>
       </c>
       <c r="B19" t="n">
@@ -2614,7 +2602,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>2024</v>
       </c>
       <c r="B20" t="n">

--- a/city_finance_analysis/data_clean/住宅商品房销售总额.xlsx
+++ b/city_finance_analysis/data_clean/住宅商品房销售总额.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,194 +429,194 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>天津</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>石家庄</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>太原</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>呼和浩特</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>沈阳</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>大连</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>长春</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>哈尔滨</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>宁波</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>合肥</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>福州</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>厦门</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>南昌</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>济南</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>青岛</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>郑州</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>长沙</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>南宁</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>海口</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>贵阳</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>昆明</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>拉萨</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>西安</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>兰州</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>西宁</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>银川</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>乌鲁木齐</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>2006</v>
       </c>
       <c r="B2" t="n">
@@ -715,7 +727,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>2007</v>
       </c>
       <c r="B3" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>2008</v>
       </c>
       <c r="B4" t="n">
@@ -937,7 +949,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>2009</v>
       </c>
       <c r="B5" t="n">
@@ -1048,7 +1060,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="B6" t="n">
@@ -1159,7 +1171,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>2011</v>
       </c>
       <c r="B7" t="n">
@@ -1270,7 +1282,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="B8" t="n">
@@ -1381,7 +1393,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>2013</v>
       </c>
       <c r="B9" t="n">
@@ -1492,7 +1504,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>2014</v>
       </c>
       <c r="B10" t="n">
@@ -1603,7 +1615,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="B11" t="n">
@@ -1714,7 +1726,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="B12" t="n">
@@ -1825,7 +1837,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
         <v>2017</v>
       </c>
       <c r="B13" t="n">
@@ -1936,7 +1948,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
         <v>2018</v>
       </c>
       <c r="B14" t="n">
@@ -2047,7 +2059,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>2019</v>
       </c>
       <c r="B15" t="n">
@@ -2158,7 +2170,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>2020</v>
       </c>
       <c r="B16" t="n">
@@ -2269,7 +2281,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>2021</v>
       </c>
       <c r="B17" t="n">
@@ -2380,7 +2392,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="B18" t="n">
@@ -2491,7 +2503,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="1" t="n">
         <v>2023</v>
       </c>
       <c r="B19" t="n">
@@ -2602,7 +2614,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="1" t="n">
         <v>2024</v>
       </c>
       <c r="B20" t="n">
